--- a/data/trans_dic/IP31KM13_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,67; 94,2</t>
+          <t>91,55; 98,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,59; 98,23</t>
+          <t>82,85; 94,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,87; 95,9</t>
+          <t>89,31; 95,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,01; 96,66</t>
+          <t>80,53; 92,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,24; 92,51</t>
+          <t>87,21; 96,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,25; 93,35</t>
+          <t>85,7; 93,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,11; 100,0</t>
+          <t>83,67; 97,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,4; 97,03</t>
+          <t>90,96; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,23; 97,57</t>
+          <t>90,23; 97,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,14; 96,58</t>
+          <t>88,34; 95,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,97; 95,36</t>
+          <t>88,07; 95,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,9; 95,44</t>
+          <t>89,66; 94,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,09; 93,8</t>
+          <t>68,76; 94,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,15; 94,65</t>
+          <t>86,08; 95,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,27; 92,75</t>
+          <t>77,96; 93,1</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,91; 95,76</t>
+          <t>81,62; 96,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,43; 95,4</t>
+          <t>82,54; 95,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,76; 94,54</t>
+          <t>85,03; 94,59</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,95; 94,11</t>
+          <t>86,18; 93,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,11; 93,25</t>
+          <t>90,18; 93,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,0; 93,03</t>
+          <t>89,23; 92,97</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91496</t>
+          <t>116316</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>129673</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221170</t>
+          <t>206338</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84085; 95814</t>
+          <t>110965; 119133</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123810; 132779</t>
+          <t>83143; 94424</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212886; 227168</t>
+          <t>197884; 211765</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>78110</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168460</t>
+          <t>166724</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82196; 90276</t>
+          <t>72378; 82960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75196; 86687</t>
+          <t>83209; 92296</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159497; 174665</t>
+          <t>158791; 172817</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>51789</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106298</t>
+          <t>102585</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45636; 50089</t>
+          <t>46723; 54402</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51988; 60482</t>
+          <t>47308; 52010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100316; 109693</t>
+          <t>97320; 105336</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>252</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>202529</t>
+          <t>182796</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>196991</t>
+          <t>163231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399521</t>
+          <t>346027</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194286; 208162</t>
+          <t>174306; 188508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189208; 202791</t>
+          <t>155559; 169138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>389231; 408666</t>
+          <t>335305; 353653</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>138311</t>
+          <t>105443</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>241081</t>
+          <t>231722</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>91353; 108343</t>
+          <t>100099; 136896</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105477; 150935</t>
+          <t>99392; 109930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206975; 255038</t>
+          <t>203520; 243037</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>62799</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62651</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125449</t>
+          <t>123314</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57812; 65971</t>
+          <t>53755; 63299</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56900; 65854</t>
+          <t>58071; 67372</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>118283; 130397</t>
+          <t>115833; 128845</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>833</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>595150</t>
+          <t>614882</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>666828</t>
+          <t>561827</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1261978</t>
+          <t>1176710</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>580276; 607161</t>
+          <t>582290; 629584</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>630628; 682913</t>
+          <t>550295; 572806</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1226029; 1281456</t>
+          <t>1147492; 1195512</t>
         </is>
       </c>
     </row>
